--- a/erp-server/erp-server-file/src/main/resources/excel/scm/assetNotice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/assetNotice.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">开模通知单号
 </t>
@@ -53,8 +53,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">一级供应商
-</t>
+    <t>项目名称</t>
+  </si>
+  <si>
+    <t>供应商名称</t>
   </si>
   <si>
     <t xml:space="preserve">计划交期
@@ -65,6 +67,33 @@
 </t>
   </si>
   <si>
+    <t>剩余数量</t>
+  </si>
+  <si>
+    <t>实际采购量</t>
+  </si>
+  <si>
+    <t>审核人（最新）</t>
+  </si>
+  <si>
+    <t>审核完成时间</t>
+  </si>
+  <si>
+    <t>申请人</t>
+  </si>
+  <si>
+    <t>采购开发</t>
+  </si>
+  <si>
+    <t>采购跟单</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -83,6 +112,9 @@
     <t>{.assetName}</t>
   </si>
   <si>
+    <t>{.projectName}</t>
+  </si>
+  <si>
     <t>{.supplierName}</t>
   </si>
   <si>
@@ -90,6 +122,27 @@
   </si>
   <si>
     <t>{.applyQty}</t>
+  </si>
+  <si>
+    <t>{.waitQty}{.realPurchaseQty}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.approveTime}</t>
+  </si>
+  <si>
+    <t>{.applyUserName}{.purchaseDevUserName}</t>
+  </si>
+  <si>
+    <t>{.purchaseFollowUserName}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1308,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
@@ -1264,18 +1317,20 @@
     <col min="4" max="4" width="19.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.125" style="1" customWidth="1"/>
-    <col min="15" max="16383" width="9" style="1"/>
+    <col min="7" max="8" width="20" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.75" style="1" customWidth="1"/>
+    <col min="13" max="14" width="24.125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15" style="1" customWidth="1"/>
+    <col min="17" max="17" width="18.125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" spans="1:22">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1303,44 +1358,91 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:19">
+    <row r="2" s="1" customFormat="1" spans="1:22">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/assetNotice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/assetNotice.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">开模通知单号
 </t>
@@ -118,7 +118,7 @@
     <t>{.supplierName}</t>
   </si>
   <si>
-    <t>{.planDeliverDate}</t>
+    <t>{.planDeliveryDate}</t>
   </si>
   <si>
     <t>{.applyQty}</t>
@@ -133,7 +133,10 @@
     <t>{.approveTime}</t>
   </si>
   <si>
-    <t>{.applyUserName}{.purchaseDevUserName}</t>
+    <t>{.applyUserName}</t>
+  </si>
+  <si>
+    <t>{.purchaseDevUserName}</t>
   </si>
   <si>
     <t>{.purchaseFollowUserName}</t>
@@ -1323,7 +1326,7 @@
     <col min="11" max="11" width="8.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="8.75" style="1" customWidth="1"/>
     <col min="13" max="14" width="24.125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="42.625" style="1" customWidth="1"/>
     <col min="16" max="16" width="15" style="1" customWidth="1"/>
     <col min="17" max="17" width="18.125" style="1" customWidth="1"/>
     <col min="18" max="18" width="19.375" style="1" customWidth="1"/>
@@ -1435,14 +1438,17 @@
       <c r="O2" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="Q2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
